--- a/HELPER scoredetail.xlsx
+++ b/HELPER scoredetail.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\DT\nfl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537AB5EB-C1C0-4B26-B6B7-D554F06CF10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56582CA-3AE2-43F9-AE6F-D83AC596D823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="2235" windowWidth="24480" windowHeight="11295" xr2:uid="{C77011C8-79D3-4A8C-A59A-B704AE48665D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C77011C8-79D3-4A8C-A59A-B704AE48665D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
-  <si>
-    <t>Home</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>Quarter</t>
   </si>
@@ -62,31 +59,97 @@
     <t>Rams</t>
   </si>
   <si>
-    <t>Falcons</t>
-  </si>
-  <si>
-    <t>Jeff Wilkins 28 yard field goal</t>
-  </si>
-  <si>
     <t>CAR</t>
   </si>
   <si>
-    <t>Jeff Wilkins 38 yard field goal</t>
-  </si>
-  <si>
-    <t>Safety,</t>
-  </si>
-  <si>
-    <t>Marc Bulger 3 yard rush (Jeff Wilkins kick)</t>
-  </si>
-  <si>
-    <t>Torry Holt 21 yard pass from Marc Bulger (Jeff Wilkins kick)</t>
-  </si>
-  <si>
-    <t>Torry Holt 14 yard pass from Marc Bulger (Jeff Wilkins kick)</t>
-  </si>
-  <si>
-    <t>Travis Fisher 74 yard interception return (Jeff Wilkins kick)</t>
+    <t>Away</t>
+  </si>
+  <si>
+    <t>Seahawks</t>
+  </si>
+  <si>
+    <t>'2012.1.09092012.Away.Lions', c(1,2,2,2,2,3,4,4,4,4), c(1.57,9.26,2.35,1.28,0.20,9.29,9.45,7.19,1.55,0.10), c(T,F,T,T,F,F,T,F,T,F), c(3,7,3,7,3,3,7,7,3,7),</t>
+  </si>
+  <si>
+    <t>Greg Zuerlein 39 yard field goal</t>
+  </si>
+  <si>
+    <t>'2012.2.16092012.Home.Redskins', c(1,1,1,2,2,2,2,3,3,4), c(14.49,9.5,0.19,8.17,6.19,1.58,0.2,10.23,5.27,14.55), c(F,T,F,T,F,T,T,T,F,T), c(7,3,7,3,7,7,3,7,7,8),</t>
+  </si>
+  <si>
+    <t>'2012.3.23092012.Away.Bears', c(1,2,2,3,4,4,4), c(10.41,1.56,0.22,6.14,9.45,9.6,2.18), c(F,F,T,T,F,F,F), c(3,7,3,3,3,7,3),</t>
+  </si>
+  <si>
+    <t>'2012.4.30092012.Home.Seahawks', c(1,1,2,2,3,3,4,4), c(10.45,4.59,1.11,0.0,13.46,4.10,13.3,6.7), c(F,T,T,T,T,F,F,T), c(7,3,7,3,3,3,3,3),</t>
+  </si>
+  <si>
+    <t>'2012.5.04102012.Home.Cardinals', c(1,1,2,4), c(12.39,3.15,10.45,11.49), c(T,F,T,T), c(7,3,3,7),</t>
+  </si>
+  <si>
+    <t>'2012.6.14102012.Away.Dolphins', c(1,1,2,2,3,4), c(12.25,5.8,5.27,4.19,9.40,8.30), c(T,T,F,F,F,T), c(3,3,7,3,7,8),</t>
+  </si>
+  <si>
+    <t>'2012.7.21102012.Home.Packers', c(1,1,1,2,3,4,4,4,4,4), c(7.38,5.23,2.17,0.40,8.4,11.52,8.50,3.6,1.49,0.15), c(T,F,F,T,F,F,T,F,F,T), c(3,7,3,3,7,3,7,7,3,7),</t>
+  </si>
+  <si>
+    <t>'2012.8.28102012.Home.Patriots', c(1,1,2,2,2,3,3,4), c(12.25,7.50,14.12,6.26,0.10,12.24,6.55,11.20), c(T,F,F,F,F,F,F,F), c(7,7,7,7,7,7,3,7),</t>
+  </si>
+  <si>
+    <t>Austin Pettis 2 yard pass from Sam Bradford (Greg Zuerlein kick)</t>
+  </si>
+  <si>
+    <t>'2012.10.11112012.Away.49ers', c(1,1,2,3,4,4,4,4), c(9.38,1.47,8.13,0.18,8.40,8.23,1.9,0.3), c(T,T,F,T,F,F,T,F), c(7,7,7,3,7,7,7,3),</t>
+  </si>
+  <si>
+    <t>'2012.11.18112012.Home.Jets', c(1,1,2,2,4,4,4), c(3.45,0.44,4.31,0.57,14.16,8.29,5.40), c(T,F,F,F,F,F,T), c(7,3,7,3,7,7,6),</t>
+  </si>
+  <si>
+    <t>'2012.12.25112012.Away.Cardinals', c(1,2,2,2,2,3,3,4), c(2.41,14.52,7.52,1.53,0.0,9.58,2.28,5.27), c(F,T,F,T,F,T,T,T), c(7,7,7,7,3,7,7,3),</t>
+  </si>
+  <si>
+    <t>'2012.13.02122012.Home.49ers', c(1,3,4,4,4,4,5), c(2.58,4.27,8.43,3.4,1.34,0.0,0.26), c(F,T,F,T,F,T,T), c(7,2,3,8,3,3,3),</t>
+  </si>
+  <si>
+    <t>'2012.14.09122012.Away.Bills', c(1,2,3,3,4), c(2.14,0.7,8.37,3.26,0.48), c(F,F,T,F,T), c(3,3,7,6,8),</t>
+  </si>
+  <si>
+    <t>Vikings</t>
+  </si>
+  <si>
+    <t>Blair Walsh 53 yard field goal</t>
+  </si>
+  <si>
+    <t>Danny Amendola 6 yard pass from Sam Bradford (Greg Zuerlein kick)</t>
+  </si>
+  <si>
+    <t>Lance Kendricks 6 yard pass from Sam Bradford (Danny Amendola pass from Sam Bradford)</t>
+  </si>
+  <si>
+    <t>Blair Walsh 51 yard field goal</t>
+  </si>
+  <si>
+    <t>'2012.15.16122012.Home.Vikings', c(1,2,2,2,2,2,2,3,4,4,4), c(7.7,12.39,12.21,9.11,8.25,3.11,0.0,5.56,13.39,7.48,5.31), c(F,T,F,F,F,F,F,F,T,T,F), c(7,7,7,3,7,3,3,3,7,8,3),</t>
+  </si>
+  <si>
+    <t>'2012.16.23122012.Away.Buccaneers', c(1,2,2,2,3,3,3), c(5.22,11.46,5.56,0.32,14.46,10.47,8.50), c(F,T,F,T,T,T,F), c(3,7,3,7,7,7,7),</t>
+  </si>
+  <si>
+    <t>Stephen Hauschka 43 yard field goal</t>
+  </si>
+  <si>
+    <t>Stephen Hauschka 49 yard field goal</t>
+  </si>
+  <si>
+    <t>Michael Robinson 10 yard pass from Russell Wilson (Stephen Hauschka kick)</t>
+  </si>
+  <si>
+    <t>Greg Zuerlein 25 yard field goal</t>
+  </si>
+  <si>
+    <t>Russell Wilson 1 yard rush (Stephen Hauschka kick)</t>
+  </si>
+  <si>
+    <t>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39), c(F,T,F,T,F,T,F), c(3,7,3,3,7,3,7),</t>
   </si>
 </sst>
 </file>
@@ -127,12 +190,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -467,58 +531,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9D3882-2A87-4C0E-8859-548E3BE7A89F}">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="B1" s="1">
-        <v>6</v>
-      </c>
-      <c r="C1" s="4">
-        <v>13102003</v>
-      </c>
-      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
+      <c r="G1" s="4">
+        <f>IF(D1&gt;8,A1,A1+1)</f>
+        <v>2012</v>
+      </c>
+      <c r="H1" t="str">
+        <f>IF(C1&lt;10,"0"&amp;C1,C1)&amp;IF(D1&lt;10,"0"&amp;D1,D1)&amp;G1</f>
+        <v>30122012</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>5.347222222222222E-2</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -528,15 +603,15 @@
       </c>
       <c r="G4">
         <f>A4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="str">
         <f>HOUR(B4)&amp;"."&amp;MINUTE(B4)</f>
-        <v>1.17</v>
+        <v>10.40</v>
       </c>
       <c r="I4" t="str">
         <f>IF(C4="Rams","T","F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="J4">
         <f>SUM(E4:F4)</f>
@@ -544,54 +619,52 @@
       </c>
       <c r="K4">
         <f>G4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="str">
         <f>H4</f>
-        <v>1.17</v>
+        <v>10.40</v>
       </c>
       <c r="M4" t="str">
         <f>I4</f>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="N4">
         <f t="shared" ref="N4" si="0">J4</f>
         <v>3</v>
       </c>
       <c r="O4" t="str">
-        <f>"'"&amp;$A$1&amp;"."&amp;$B$1&amp;"."&amp;$C$1&amp;"."&amp;$E$1&amp;"."&amp;$D$1&amp;"', c("&amp;K4&amp;"), c("&amp;L4&amp;"), c("&amp;M4&amp;"), c("&amp;N4&amp;")"</f>
-        <v>'2003.6.13102003.Home.Falcons', c(1), c(1.17), c(T), c(3)</v>
+        <f>"'"&amp;$A$1&amp;"."&amp;$B$1&amp;"."&amp;$H$1&amp;"."&amp;$F$1&amp;"."&amp;$E$1&amp;"', c("&amp;K4&amp;"), c("&amp;L4&amp;"), c("&amp;M4&amp;"), c("&amp;N4&amp;"),"</f>
+        <v>'2012.17.30122012.Away.Seahawks', c(2), c(10.40), c(F), c(3),</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
+      <c r="A5" s="1"/>
       <c r="B5" s="3">
-        <v>5.6944444444444443E-2</v>
+        <v>0.25208333333333333</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F5" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <f>IF(A5="",G4,A5)</f>
         <v>2</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" ref="H5:H9" si="1">HOUR(B5)&amp;"."&amp;MINUTE(B5)</f>
-        <v>1.22</v>
+        <f t="shared" ref="H5" si="1">HOUR(B5)&amp;"."&amp;MINUTE(B5)</f>
+        <v>6.3</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" ref="I5:I9" si="2">IF(C5="Rams","T","F")</f>
+        <f t="shared" ref="I5" si="2">IF(C5="Rams","T","F")</f>
         <v>T</v>
       </c>
       <c r="J5">
@@ -600,23 +673,23 @@
       </c>
       <c r="K5" t="str">
         <f>K4&amp;","&amp;G5</f>
-        <v>1,2</v>
+        <v>2,2</v>
       </c>
       <c r="L5" t="str">
         <f>L4&amp;","&amp;H5</f>
-        <v>1.17,1.22</v>
+        <v>10.40,6.3</v>
       </c>
       <c r="M5" t="str">
         <f>M4&amp;","&amp;I5</f>
-        <v>T,T</v>
+        <v>F,T</v>
       </c>
       <c r="N5" t="str">
         <f>N4&amp;","&amp;J5</f>
         <v>3,7</v>
       </c>
       <c r="O5" t="str">
-        <f t="shared" ref="O5:O9" si="3">"'"&amp;$A$1&amp;"."&amp;$B$1&amp;"."&amp;$C$1&amp;"."&amp;$E$1&amp;"."&amp;$D$1&amp;"', c("&amp;K5&amp;"), c("&amp;L5&amp;"), c("&amp;M5&amp;"), c("&amp;N5&amp;")"</f>
-        <v>'2003.6.13102003.Home.Falcons', c(1,2), c(1.17,1.22), c(T,T), c(3,7)</v>
+        <f t="shared" ref="O5:O14" si="3">"'"&amp;$A$1&amp;"."&amp;$B$1&amp;"."&amp;$H$1&amp;"."&amp;$F$1&amp;"."&amp;$E$1&amp;"', c("&amp;K5&amp;"), c("&amp;L5&amp;"), c("&amp;M5&amp;"), c("&amp;N5&amp;"),"</f>
+        <v>'2012.17.30122012.Away.Seahawks', c(2,2), c(10.40,6.3), c(F,T), c(3,7),</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -624,283 +697,489 @@
         <v>3</v>
       </c>
       <c r="B6" s="2">
-        <v>0.51111111111111107</v>
+        <v>0.44513888888888886</v>
       </c>
       <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
         <v>6</v>
       </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>17</v>
-      </c>
       <c r="G6">
-        <f t="shared" ref="G6:G10" si="4">IF(A6="",G5,A6)</f>
+        <f t="shared" ref="G6" si="4">IF(A6="",G5,A6)</f>
         <v>3</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" ref="H6:H10" si="5">HOUR(B6)&amp;"."&amp;MINUTE(B6)</f>
-        <v>12.16</v>
+        <f t="shared" ref="H6" si="5">HOUR(B6)&amp;"."&amp;MINUTE(B6)</f>
+        <v>10.41</v>
       </c>
       <c r="I6" t="str">
-        <f t="shared" ref="I6:I10" si="6">IF(C6="Rams","T","F")</f>
-        <v>T</v>
+        <f t="shared" ref="I6" si="6">IF(C6="Rams","T","F")</f>
+        <v>F</v>
       </c>
       <c r="J6">
-        <f t="shared" ref="J6:J10" si="7">SUM(E6:F6)-SUM(E5:F5)</f>
-        <v>7</v>
+        <f t="shared" ref="J6" si="7">SUM(E6:F6)-SUM(E5:F5)</f>
+        <v>3</v>
       </c>
       <c r="K6" t="str">
-        <f t="shared" ref="K6:K10" si="8">K5&amp;","&amp;G6</f>
-        <v>1,2,3</v>
+        <f t="shared" ref="K6" si="8">K5&amp;","&amp;G6</f>
+        <v>2,2,3</v>
       </c>
       <c r="L6" t="str">
-        <f t="shared" ref="L6:L10" si="9">L5&amp;","&amp;H6</f>
-        <v>1.17,1.22,12.16</v>
+        <f t="shared" ref="L6" si="9">L5&amp;","&amp;H6</f>
+        <v>10.40,6.3,10.41</v>
       </c>
       <c r="M6" t="str">
-        <f t="shared" ref="M6:M10" si="10">M5&amp;","&amp;I6</f>
-        <v>T,T,T</v>
+        <f t="shared" ref="M6" si="10">M5&amp;","&amp;I6</f>
+        <v>F,T,F</v>
       </c>
       <c r="N6" t="str">
-        <f t="shared" ref="N6:N10" si="11">N5&amp;","&amp;J6</f>
-        <v>3,7,7</v>
+        <f t="shared" ref="N6" si="11">N5&amp;","&amp;J6</f>
+        <v>3,7,3</v>
       </c>
       <c r="O6" t="str">
-        <f t="shared" ref="O6:O10" si="12">"'"&amp;$A$1&amp;"."&amp;$B$1&amp;"."&amp;$C$1&amp;"."&amp;$E$1&amp;"."&amp;$D$1&amp;"', c("&amp;K6&amp;"), c("&amp;L6&amp;"), c("&amp;M6&amp;"), c("&amp;N6&amp;")"</f>
-        <v>'2003.6.13102003.Home.Falcons', c(1,2,3), c(1.17,1.22,12.16), c(T,T,T), c(3,7,7)</v>
+        <f t="shared" si="3"/>
+        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3), c(10.40,6.3,10.41), c(F,T,F), c(3,7,3),</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B7" s="2">
-        <v>9.375E-2</v>
+        <v>0.2298611111111111</v>
       </c>
       <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>19</v>
-      </c>
       <c r="G7">
-        <f t="shared" ref="G7:G12" si="13">IF(A7="",G6,A7)</f>
+        <f t="shared" ref="G7" si="12">IF(A7="",G6,A7)</f>
         <v>3</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" ref="H7:H12" si="14">HOUR(B7)&amp;"."&amp;MINUTE(B7)</f>
-        <v>2.15</v>
+        <f t="shared" ref="H7" si="13">HOUR(B7)&amp;"."&amp;MINUTE(B7)</f>
+        <v>5.31</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" ref="I7:I12" si="15">IF(C7="Rams","T","F")</f>
+        <f t="shared" ref="I7" si="14">IF(C7="Rams","T","F")</f>
         <v>T</v>
       </c>
       <c r="J7">
-        <f t="shared" ref="J7:J12" si="16">SUM(E7:F7)-SUM(E6:F6)</f>
-        <v>2</v>
+        <f t="shared" ref="J7" si="15">SUM(E7:F7)-SUM(E6:F6)</f>
+        <v>3</v>
       </c>
       <c r="K7" t="str">
-        <f t="shared" ref="K7:K12" si="17">K6&amp;","&amp;G7</f>
-        <v>1,2,3,3</v>
+        <f t="shared" ref="K7" si="16">K6&amp;","&amp;G7</f>
+        <v>2,2,3,3</v>
       </c>
       <c r="L7" t="str">
-        <f t="shared" ref="L7:L12" si="18">L6&amp;","&amp;H7</f>
-        <v>1.17,1.22,12.16,2.15</v>
+        <f t="shared" ref="L7" si="17">L6&amp;","&amp;H7</f>
+        <v>10.40,6.3,10.41,5.31</v>
       </c>
       <c r="M7" t="str">
-        <f t="shared" ref="M7:M12" si="19">M6&amp;","&amp;I7</f>
-        <v>T,T,T,T</v>
+        <f t="shared" ref="M7" si="18">M6&amp;","&amp;I7</f>
+        <v>F,T,F,T</v>
       </c>
       <c r="N7" t="str">
-        <f t="shared" ref="N7:N12" si="20">N6&amp;","&amp;J7</f>
-        <v>3,7,7,2</v>
+        <f t="shared" ref="N7" si="19">N6&amp;","&amp;J7</f>
+        <v>3,7,3,3</v>
       </c>
       <c r="O7" t="str">
-        <f t="shared" ref="O7:O12" si="21">"'"&amp;$A$1&amp;"."&amp;$B$1&amp;"."&amp;$C$1&amp;"."&amp;$E$1&amp;"."&amp;$D$1&amp;"', c("&amp;K7&amp;"), c("&amp;L7&amp;"), c("&amp;M7&amp;"), c("&amp;N7&amp;")"</f>
-        <v>'2003.6.13102003.Home.Falcons', c(1,2,3,3), c(1.17,1.22,12.16,2.15), c(T,T,T,T), c(3,7,7,2)</v>
+        <f t="shared" si="3"/>
+        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3), c(10.40,6.3,10.41,5.31), c(F,T,F,T), c(3,7,3,3),</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="B8" s="2">
+        <v>8.9583333333333334E-2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <f>IF(A8="",G7,A8)</f>
+        <v>3</v>
+      </c>
+      <c r="H8" t="str">
+        <f>HOUR(B8)&amp;"."&amp;MINUTE(B8)</f>
+        <v>2.9</v>
+      </c>
+      <c r="I8" t="str">
+        <f>IF(C8="Rams","T","F")</f>
+        <v>F</v>
+      </c>
+      <c r="J8">
+        <f>SUM(E8:F8)-SUM(E7:F7)</f>
+        <v>7</v>
+      </c>
+      <c r="K8" t="str">
+        <f>K7&amp;","&amp;G8</f>
+        <v>2,2,3,3,3</v>
+      </c>
+      <c r="L8" t="str">
+        <f>L7&amp;","&amp;H8</f>
+        <v>10.40,6.3,10.41,5.31,2.9</v>
+      </c>
+      <c r="M8" t="str">
+        <f>M7&amp;","&amp;I8</f>
+        <v>F,T,F,T,F</v>
+      </c>
+      <c r="N8" t="str">
+        <f>N7&amp;","&amp;J8</f>
+        <v>3,7,3,3,7</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="3"/>
+        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3), c(10.40,6.3,10.41,5.31,2.9), c(F,T,F,T,F), c(3,7,3,3,7),</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>4</v>
       </c>
-      <c r="B8" s="2">
-        <v>0.44722222222222224</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>26</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="13"/>
+      <c r="B9" s="2">
+        <v>0.47430555555555554</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9">
+        <v>13</v>
+      </c>
+      <c r="F9">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <f t="shared" ref="G9:G14" si="20">IF(A9="",G8,A9)</f>
         <v>4</v>
       </c>
-      <c r="H8" t="str">
-        <f t="shared" si="14"/>
-        <v>10.44</v>
-      </c>
-      <c r="I8" t="str">
-        <f t="shared" si="15"/>
+      <c r="H9" t="str">
+        <f t="shared" ref="H9:H14" si="21">HOUR(B9)&amp;"."&amp;MINUTE(B9)</f>
+        <v>11.23</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" ref="I9:I14" si="22">IF(C9="Rams","T","F")</f>
         <v>T</v>
       </c>
-      <c r="J8">
-        <f t="shared" si="16"/>
-        <v>7</v>
-      </c>
-      <c r="K8" t="str">
-        <f t="shared" si="17"/>
-        <v>1,2,3,3,4</v>
-      </c>
-      <c r="L8" t="str">
-        <f t="shared" si="18"/>
-        <v>1.17,1.22,12.16,2.15,10.44</v>
-      </c>
-      <c r="M8" t="str">
-        <f t="shared" si="19"/>
-        <v>T,T,T,T,T</v>
-      </c>
-      <c r="N8" t="str">
-        <f t="shared" si="20"/>
-        <v>3,7,7,2,7</v>
-      </c>
-      <c r="O8" t="str">
-        <f t="shared" si="21"/>
-        <v>'2003.6.13102003.Home.Falcons', c(1,2,3,3,4), c(1.17,1.22,12.16,2.15,10.44), c(T,T,T,T,T), c(3,7,7,2,7)</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B9" s="2">
-        <v>0.15625</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>29</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="H9" t="str">
-        <f t="shared" si="14"/>
-        <v>3.45</v>
-      </c>
-      <c r="I9" t="str">
-        <f t="shared" si="15"/>
-        <v>T</v>
-      </c>
       <c r="J9">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="J9:J14" si="23">SUM(E9:F9)-SUM(E8:F8)</f>
         <v>3</v>
       </c>
       <c r="K9" t="str">
-        <f t="shared" si="17"/>
-        <v>1,2,3,3,4,4</v>
+        <f t="shared" ref="K9:K14" si="24">K8&amp;","&amp;G9</f>
+        <v>2,2,3,3,3,4</v>
       </c>
       <c r="L9" t="str">
-        <f t="shared" si="18"/>
-        <v>1.17,1.22,12.16,2.15,10.44,3.45</v>
+        <f t="shared" ref="L9:L14" si="25">L8&amp;","&amp;H9</f>
+        <v>10.40,6.3,10.41,5.31,2.9,11.23</v>
       </c>
       <c r="M9" t="str">
-        <f t="shared" si="19"/>
-        <v>T,T,T,T,T,T</v>
+        <f t="shared" ref="M9:M14" si="26">M8&amp;","&amp;I9</f>
+        <v>F,T,F,T,F,T</v>
       </c>
       <c r="N9" t="str">
-        <f t="shared" si="20"/>
-        <v>3,7,7,2,7,3</v>
+        <f t="shared" ref="N9:N14" si="27">N8&amp;","&amp;J9</f>
+        <v>3,7,3,3,7,3</v>
       </c>
       <c r="O9" t="str">
-        <f t="shared" si="21"/>
-        <v>'2003.6.13102003.Home.Falcons', c(1,2,3,3,4,4), c(1.17,1.22,12.16,2.15,10.44,3.45), c(T,T,T,T,T,T), c(3,7,7,2,7,3)</v>
+        <f t="shared" si="3"/>
+        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4), c(10.40,6.3,10.41,5.31,2.9,11.23), c(F,T,F,T,F,T), c(3,7,3,3,7,3),</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B10" s="2">
-        <v>6.458333333333334E-2</v>
+        <v>6.8750000000000006E-2</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="20"/>
+        <v>4</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="21"/>
+        <v>1.39</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="22"/>
+        <v>F</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="24"/>
+        <v>2,2,3,3,3,4,4</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="25"/>
+        <v>10.40,6.3,10.41,5.31,2.9,11.23,1.39</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="26"/>
+        <v>F,T,F,T,F,T,F</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="27"/>
+        <v>3,7,3,3,7,3,7</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="3"/>
+        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39), c(F,T,F,T,F,T,F), c(3,7,3,3,7,3,7),</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.24722222222222223</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11">
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="20"/>
+        <v>3</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="21"/>
+        <v>5.56</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="22"/>
+        <v>F</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="K11" t="str">
+        <f t="shared" si="24"/>
+        <v>2,2,3,3,3,4,4,3</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="25"/>
+        <v>10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="26"/>
+        <v>F,T,F,T,F,T,F,F</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="27"/>
+        <v>3,7,3,3,7,3,7,7</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="3"/>
+        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4,3), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56), c(F,T,F,T,F,T,F,F), c(3,7,3,3,7,3,7,7),</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.56874999999999998</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12">
+        <v>33</v>
+      </c>
+      <c r="F12">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="20"/>
+        <v>4</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="21"/>
+        <v>13.39</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="22"/>
+        <v>T</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="24"/>
+        <v>2,2,3,3,3,4,4,3,4</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="25"/>
+        <v>10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="26"/>
+        <v>F,T,F,T,F,T,F,F,T</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="27"/>
+        <v>3,7,3,3,7,3,7,7,7</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" si="3"/>
+        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4,3,4), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39), c(F,T,F,T,F,T,F,F,T), c(3,7,3,3,7,3,7,7,7),</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B13" s="2">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13">
+        <v>33</v>
+      </c>
+      <c r="F13">
+        <v>22</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="20"/>
+        <v>4</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="21"/>
+        <v>7.48</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="22"/>
+        <v>T</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="23"/>
+        <v>8</v>
+      </c>
+      <c r="K13" t="str">
+        <f t="shared" si="24"/>
+        <v>2,2,3,3,3,4,4,3,4,4</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="25"/>
+        <v>10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39,7.48</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" si="26"/>
+        <v>F,T,F,T,F,T,F,F,T,T</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="27"/>
+        <v>3,7,3,3,7,3,7,7,7,8</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="3"/>
+        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4,3,4,4), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39,7.48), c(F,T,F,T,F,T,F,F,T,T), c(3,7,3,3,7,3,7,7,7,8),</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B14" s="2">
+        <v>0.2298611111111111</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14">
         <v>36</v>
       </c>
-      <c r="G10">
-        <f t="shared" si="13"/>
+      <c r="F14">
+        <v>22</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
-      <c r="H10" t="str">
-        <f t="shared" si="14"/>
-        <v>1.33</v>
-      </c>
-      <c r="I10" t="str">
-        <f t="shared" si="15"/>
-        <v>T</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="16"/>
-        <v>7</v>
-      </c>
-      <c r="K10" t="str">
-        <f t="shared" si="17"/>
-        <v>1,2,3,3,4,4,4</v>
-      </c>
-      <c r="L10" t="str">
-        <f t="shared" si="18"/>
-        <v>1.17,1.22,12.16,2.15,10.44,3.45,1.33</v>
-      </c>
-      <c r="M10" t="str">
-        <f t="shared" si="19"/>
-        <v>T,T,T,T,T,T,T</v>
-      </c>
-      <c r="N10" t="str">
-        <f t="shared" si="20"/>
-        <v>3,7,7,2,7,3,7</v>
-      </c>
-      <c r="O10" t="str">
+      <c r="H14" t="str">
         <f t="shared" si="21"/>
-        <v>'2003.6.13102003.Home.Falcons', c(1,2,3,3,4,4,4), c(1.17,1.22,12.16,2.15,10.44,3.45,1.33), c(T,T,T,T,T,T,T), c(3,7,7,2,7,3,7)</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B14" s="2"/>
+        <v>5.31</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="22"/>
+        <v>F</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="24"/>
+        <v>2,2,3,3,3,4,4,3,4,4,4</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="25"/>
+        <v>10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39,7.48,5.31</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="26"/>
+        <v>F,T,F,T,F,T,F,F,T,T,F</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="27"/>
+        <v>3,7,3,3,7,3,7,7,7,8,3</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="3"/>
+        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4,3,4,4,4), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39,7.48,5.31), c(F,T,F,T,F,T,F,F,T,T,F), c(3,7,3,3,7,3,7,7,7,8,3),</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>
@@ -908,16 +1187,98 @@
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B19" s="2"/>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="15:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="15:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="15:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="15:15" x14ac:dyDescent="0.2">
+      <c r="O36" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="15:15" x14ac:dyDescent="0.2">
+      <c r="O37" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{D805864C-A3B5-4395-9A48-009A3AECAD44}">
+      <formula1>"Home,Away"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/HELPER scoredetail.xlsx
+++ b/HELPER scoredetail.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\DT\nfl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56582CA-3AE2-43F9-AE6F-D83AC596D823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD4DEF2-F481-4468-99FD-02C800722827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C77011C8-79D3-4A8C-A59A-B704AE48665D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>Quarter</t>
   </si>
@@ -62,94 +62,82 @@
     <t>CAR</t>
   </si>
   <si>
+    <t>Gerald Everett 40 yard pass from Jared Goff (Greg Zuerlein kick)</t>
+  </si>
+  <si>
     <t>Away</t>
   </si>
   <si>
+    <t>Buccaneers</t>
+  </si>
+  <si>
+    <t>Matt Gay 21 yard field goal</t>
+  </si>
+  <si>
+    <t>Ndamukong Suh 37 yard fumble return (Matt Gay kick)</t>
+  </si>
+  <si>
     <t>Seahawks</t>
   </si>
   <si>
-    <t>'2012.1.09092012.Away.Lions', c(1,2,2,2,2,3,4,4,4,4), c(1.57,9.26,2.35,1.28,0.20,9.29,9.45,7.19,1.55,0.10), c(T,F,T,T,F,F,T,F,T,F), c(3,7,3,7,3,3,7,7,3,7),</t>
-  </si>
-  <si>
-    <t>Greg Zuerlein 39 yard field goal</t>
-  </si>
-  <si>
-    <t>'2012.2.16092012.Home.Redskins', c(1,1,1,2,2,2,2,3,3,4), c(14.49,9.5,0.19,8.17,6.19,1.58,0.2,10.23,5.27,14.55), c(F,T,F,T,F,T,T,T,F,T), c(7,3,7,3,7,7,3,7,7,8),</t>
-  </si>
-  <si>
-    <t>'2012.3.23092012.Away.Bears', c(1,2,2,3,4,4,4), c(10.41,1.56,0.22,6.14,9.45,9.6,2.18), c(F,F,T,T,F,F,F), c(3,7,3,3,3,7,3),</t>
-  </si>
-  <si>
-    <t>'2012.4.30092012.Home.Seahawks', c(1,1,2,2,3,3,4,4), c(10.45,4.59,1.11,0.0,13.46,4.10,13.3,6.7), c(F,T,T,T,T,F,F,T), c(7,3,7,3,3,3,3,3),</t>
-  </si>
-  <si>
-    <t>'2012.5.04102012.Home.Cardinals', c(1,1,2,4), c(12.39,3.15,10.45,11.49), c(T,F,T,T), c(7,3,3,7),</t>
-  </si>
-  <si>
-    <t>'2012.6.14102012.Away.Dolphins', c(1,1,2,2,3,4), c(12.25,5.8,5.27,4.19,9.40,8.30), c(T,T,F,F,F,T), c(3,3,7,3,7,8),</t>
-  </si>
-  <si>
-    <t>'2012.7.21102012.Home.Packers', c(1,1,1,2,3,4,4,4,4,4), c(7.38,5.23,2.17,0.40,8.4,11.52,8.50,3.6,1.49,0.15), c(T,F,F,T,F,F,T,F,F,T), c(3,7,3,3,7,3,7,7,3,7),</t>
-  </si>
-  <si>
-    <t>'2012.8.28102012.Home.Patriots', c(1,1,2,2,2,3,3,4), c(12.25,7.50,14.12,6.26,0.10,12.24,6.55,11.20), c(T,F,F,F,F,F,F,F), c(7,7,7,7,7,7,3,7),</t>
-  </si>
-  <si>
-    <t>Austin Pettis 2 yard pass from Sam Bradford (Greg Zuerlein kick)</t>
-  </si>
-  <si>
-    <t>'2012.10.11112012.Away.49ers', c(1,1,2,3,4,4,4,4), c(9.38,1.47,8.13,0.18,8.40,8.23,1.9,0.3), c(T,T,F,T,F,F,T,F), c(7,7,7,3,7,7,7,3),</t>
-  </si>
-  <si>
-    <t>'2012.11.18112012.Home.Jets', c(1,1,2,2,4,4,4), c(3.45,0.44,4.31,0.57,14.16,8.29,5.40), c(T,F,F,F,F,F,T), c(7,3,7,3,7,7,6),</t>
-  </si>
-  <si>
-    <t>'2012.12.25112012.Away.Cardinals', c(1,2,2,2,2,3,3,4), c(2.41,14.52,7.52,1.53,0.0,9.58,2.28,5.27), c(F,T,F,T,F,T,T,T), c(7,7,7,7,3,7,7,3),</t>
-  </si>
-  <si>
-    <t>'2012.13.02122012.Home.49ers', c(1,3,4,4,4,4,5), c(2.58,4.27,8.43,3.4,1.34,0.0,0.26), c(F,T,F,T,F,T,T), c(7,2,3,8,3,3,3),</t>
-  </si>
-  <si>
-    <t>'2012.14.09122012.Away.Bills', c(1,2,3,3,4), c(2.14,0.7,8.37,3.26,0.48), c(F,F,T,F,T), c(3,3,7,6,8),</t>
-  </si>
-  <si>
-    <t>Vikings</t>
-  </si>
-  <si>
-    <t>Blair Walsh 53 yard field goal</t>
-  </si>
-  <si>
-    <t>Danny Amendola 6 yard pass from Sam Bradford (Greg Zuerlein kick)</t>
-  </si>
-  <si>
-    <t>Lance Kendricks 6 yard pass from Sam Bradford (Danny Amendola pass from Sam Bradford)</t>
-  </si>
-  <si>
-    <t>Blair Walsh 51 yard field goal</t>
-  </si>
-  <si>
-    <t>'2012.15.16122012.Home.Vikings', c(1,2,2,2,2,2,2,3,4,4,4), c(7.7,12.39,12.21,9.11,8.25,3.11,0.0,5.56,13.39,7.48,5.31), c(F,T,F,F,F,F,F,F,T,T,F), c(7,7,7,3,7,3,3,3,7,8,3),</t>
-  </si>
-  <si>
-    <t>'2012.16.23122012.Away.Buccaneers', c(1,2,2,2,3,3,3), c(5.22,11.46,5.56,0.32,14.46,10.47,8.50), c(F,T,F,T,T,T,F), c(3,7,3,7,7,7,7),</t>
-  </si>
-  <si>
-    <t>Stephen Hauschka 43 yard field goal</t>
-  </si>
-  <si>
-    <t>Stephen Hauschka 49 yard field goal</t>
-  </si>
-  <si>
-    <t>Michael Robinson 10 yard pass from Russell Wilson (Stephen Hauschka kick)</t>
-  </si>
-  <si>
-    <t>Greg Zuerlein 25 yard field goal</t>
-  </si>
-  <si>
-    <t>Russell Wilson 1 yard rush (Stephen Hauschka kick)</t>
-  </si>
-  <si>
-    <t>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39), c(F,T,F,T,F,T,F), c(3,7,3,3,7,3,7),</t>
+    <t>Ravens</t>
+  </si>
+  <si>
+    <t>Lions</t>
+  </si>
+  <si>
+    <t>Broncos</t>
+  </si>
+  <si>
+    <t>Tylan Wallace 76 yard punt return</t>
+  </si>
+  <si>
+    <t>Harrison Mevis 40 yard field goal</t>
+  </si>
+  <si>
+    <t>David Montgomery 1 yard rush (Jake Bates kick)</t>
+  </si>
+  <si>
+    <t>Jaxon Smith-Njigba 4 yard pass from Sam Darnold (Eric Saubert pass from Sam Darnold)</t>
+  </si>
+  <si>
+    <t>Harrison Mevis 35 yard field goal</t>
+  </si>
+  <si>
+    <t>Colby Parkinson 19 yard pass from Matthew Stafford (Harrison Mevis kick)</t>
+  </si>
+  <si>
+    <t>'2026.1.10092026.Home.49ers', c(1,2,2,3,4,4), c(6.15,14.57,4.28,11.3,12.57,9.43), c(F,T,F,F,F,F), c(3,7,7,7,7,3),</t>
+  </si>
+  <si>
+    <t>'2026.2.21092026.Home.Giants', c(1,2,2,3,3,4), c(0.11,11.7,0.25,6.21,3.49,8.57), c(T,T,F,T,F,T), c(7,7,3,7,3,7),</t>
+  </si>
+  <si>
+    <t>Tyler Higbee 5 yard pass from Matthew Stafford (Harrison Mevis kick)</t>
+  </si>
+  <si>
+    <t>Harrison Mevis 36 yard field goal</t>
+  </si>
+  <si>
+    <t>Pat Bryant 5 yard pass from Bo Nix (Jaylen Waddle pass from Bo Nix)</t>
+  </si>
+  <si>
+    <t>Nate Adkins 8 yard pass from Bo Nix (Pat Bryant pass from Bo Nix)</t>
+  </si>
+  <si>
+    <t>Harrison Mevis 48 yard field goal</t>
+  </si>
+  <si>
+    <t>Talanoa Hufanga 66 yard interception return (Wil Lutz kick)</t>
+  </si>
+  <si>
+    <t>Konata Mumpfield 48 yard pass from Matthew Stafford (Harrison Mevis kick)</t>
+  </si>
+  <si>
+    <t>Bo Nix 1 yard rush (Wil Lutz kick)</t>
+  </si>
+  <si>
+    <t>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4,4,4,4), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47), c(T,T,T,T,F,F,T,F,T,F), c(7,3,3,3,8,8,3,7,7,7),</t>
   </si>
 </sst>
 </file>
@@ -164,7 +152,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -174,6 +162,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -190,13 +184,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -531,35 +526,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9D3882-2A87-4C0E-8859-548E3BE7A89F}">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1">
-        <v>2012</v>
+        <v>2026</v>
       </c>
       <c r="B1" s="1">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="G1" s="4">
         <f>IF(D1&gt;8,A1,A1+1)</f>
-        <v>2012</v>
+        <v>2026</v>
       </c>
       <c r="H1" t="str">
         <f>IF(C1&lt;10,"0"&amp;C1,C1)&amp;IF(D1&lt;10,"0"&amp;D1,D1)&amp;G1</f>
-        <v>30122012</v>
+        <v>27092026</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -584,76 +579,78 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="3">
-        <v>0.44444444444444442</v>
+        <v>0.2048611111111111</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1">
+        <v>7</v>
+      </c>
+      <c r="F4" s="1">
         <v>0</v>
-      </c>
-      <c r="F4" s="1">
-        <v>3</v>
       </c>
       <c r="G4">
         <f>A4</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="str">
         <f>HOUR(B4)&amp;"."&amp;MINUTE(B4)</f>
-        <v>10.40</v>
+        <v>4.55</v>
       </c>
       <c r="I4" t="str">
         <f>IF(C4="Rams","T","F")</f>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="J4">
         <f>SUM(E4:F4)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K4">
         <f>G4</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" t="str">
         <f>H4</f>
-        <v>10.40</v>
+        <v>4.55</v>
       </c>
       <c r="M4" t="str">
         <f>I4</f>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="N4">
         <f t="shared" ref="N4" si="0">J4</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O4" t="str">
         <f>"'"&amp;$A$1&amp;"."&amp;$B$1&amp;"."&amp;$H$1&amp;"."&amp;$F$1&amp;"."&amp;$E$1&amp;"', c("&amp;K4&amp;"), c("&amp;L4&amp;"), c("&amp;M4&amp;"), c("&amp;N4&amp;"),"</f>
-        <v>'2012.17.30122012.Away.Seahawks', c(2), c(10.40), c(F), c(3),</v>
+        <v>'2026.3.27092026.Away.Broncos', c(1), c(4.55), c(T), c(7),</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
       <c r="B5" s="3">
-        <v>0.25208333333333333</v>
+        <v>0.55347222222222225</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <f>IF(A5="",G4,A5)</f>
@@ -661,7 +658,7 @@
       </c>
       <c r="H5" t="str">
         <f t="shared" ref="H5" si="1">HOUR(B5)&amp;"."&amp;MINUTE(B5)</f>
-        <v>6.3</v>
+        <v>13.17</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" ref="I5" si="2">IF(C5="Rams","T","F")</f>
@@ -669,59 +666,56 @@
       </c>
       <c r="J5">
         <f>SUM(E5:F5)-SUM(E4:F4)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K5" t="str">
         <f>K4&amp;","&amp;G5</f>
-        <v>2,2</v>
+        <v>1,2</v>
       </c>
       <c r="L5" t="str">
         <f>L4&amp;","&amp;H5</f>
-        <v>10.40,6.3</v>
+        <v>4.55,13.17</v>
       </c>
       <c r="M5" t="str">
         <f>M4&amp;","&amp;I5</f>
-        <v>F,T</v>
+        <v>T,T</v>
       </c>
       <c r="N5" t="str">
         <f>N4&amp;","&amp;J5</f>
-        <v>3,7</v>
+        <v>7,3</v>
       </c>
       <c r="O5" t="str">
         <f t="shared" ref="O5:O14" si="3">"'"&amp;$A$1&amp;"."&amp;$B$1&amp;"."&amp;$H$1&amp;"."&amp;$F$1&amp;"."&amp;$E$1&amp;"', c("&amp;K5&amp;"), c("&amp;L5&amp;"), c("&amp;M5&amp;"), c("&amp;N5&amp;"),"</f>
-        <v>'2012.17.30122012.Away.Seahawks', c(2,2), c(10.40,6.3), c(F,T), c(3,7),</v>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2), c(4.55,13.17), c(T,T), c(7,3),</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>3</v>
-      </c>
       <c r="B6" s="2">
-        <v>0.44513888888888886</v>
+        <v>0.19652777777777777</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <f t="shared" ref="G6" si="4">IF(A6="",G5,A6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" ref="H6" si="5">HOUR(B6)&amp;"."&amp;MINUTE(B6)</f>
-        <v>10.41</v>
+        <v>4.43</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" ref="I6" si="6">IF(C6="Rams","T","F")</f>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="J6">
         <f t="shared" ref="J6" si="7">SUM(E6:F6)-SUM(E5:F5)</f>
@@ -729,48 +723,48 @@
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6" si="8">K5&amp;","&amp;G6</f>
-        <v>2,2,3</v>
+        <v>1,2,2</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" ref="L6" si="9">L5&amp;","&amp;H6</f>
-        <v>10.40,6.3,10.41</v>
+        <v>4.55,13.17,4.43</v>
       </c>
       <c r="M6" t="str">
         <f t="shared" ref="M6" si="10">M5&amp;","&amp;I6</f>
-        <v>F,T,F</v>
+        <v>T,T,T</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" ref="N6" si="11">N5&amp;","&amp;J6</f>
-        <v>3,7,3</v>
+        <v>7,3,3</v>
       </c>
       <c r="O6" t="str">
         <f t="shared" si="3"/>
-        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3), c(10.40,6.3,10.41), c(F,T,F), c(3,7,3),</v>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2), c(4.55,13.17,4.43), c(T,T,T), c(7,3,3),</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B7" s="2">
-        <v>0.2298611111111111</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <f t="shared" ref="G7" si="12">IF(A7="",G6,A7)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" ref="H7" si="13">HOUR(B7)&amp;"."&amp;MINUTE(B7)</f>
-        <v>5.31</v>
+        <v>0.0</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" ref="I7" si="14">IF(C7="Rams","T","F")</f>
@@ -782,40 +776,43 @@
       </c>
       <c r="K7" t="str">
         <f t="shared" ref="K7" si="16">K6&amp;","&amp;G7</f>
-        <v>2,2,3,3</v>
+        <v>1,2,2,2</v>
       </c>
       <c r="L7" t="str">
         <f t="shared" ref="L7" si="17">L6&amp;","&amp;H7</f>
-        <v>10.40,6.3,10.41,5.31</v>
+        <v>4.55,13.17,4.43,0.0</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" ref="M7" si="18">M6&amp;","&amp;I7</f>
-        <v>F,T,F,T</v>
+        <v>T,T,T,T</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" ref="N7" si="19">N6&amp;","&amp;J7</f>
-        <v>3,7,3,3</v>
+        <v>7,3,3,3</v>
       </c>
       <c r="O7" t="str">
         <f t="shared" si="3"/>
-        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3), c(10.40,6.3,10.41,5.31), c(F,T,F,T), c(3,7,3,3),</v>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2), c(4.55,13.17,4.43,0.0), c(T,T,T,T), c(7,3,3,3),</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>3</v>
+      </c>
       <c r="B8" s="2">
-        <v>8.9583333333333334E-2</v>
+        <v>0.32222222222222224</v>
       </c>
       <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>16</v>
+      </c>
+      <c r="F8">
         <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>13</v>
       </c>
       <c r="G8">
         <f>IF(A8="",G7,A8)</f>
@@ -823,7 +820,7 @@
       </c>
       <c r="H8" t="str">
         <f>HOUR(B8)&amp;"."&amp;MINUTE(B8)</f>
-        <v>2.9</v>
+        <v>7.44</v>
       </c>
       <c r="I8" t="str">
         <f>IF(C8="Rams","T","F")</f>
@@ -831,100 +828,100 @@
       </c>
       <c r="J8">
         <f>SUM(E8:F8)-SUM(E7:F7)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8" t="str">
         <f>K7&amp;","&amp;G8</f>
-        <v>2,2,3,3,3</v>
+        <v>1,2,2,2,3</v>
       </c>
       <c r="L8" t="str">
         <f>L7&amp;","&amp;H8</f>
-        <v>10.40,6.3,10.41,5.31,2.9</v>
+        <v>4.55,13.17,4.43,0.0,7.44</v>
       </c>
       <c r="M8" t="str">
         <f>M7&amp;","&amp;I8</f>
-        <v>F,T,F,T,F</v>
+        <v>T,T,T,T,F</v>
       </c>
       <c r="N8" t="str">
         <f>N7&amp;","&amp;J8</f>
-        <v>3,7,3,3,7</v>
+        <v>7,3,3,3,8</v>
       </c>
       <c r="O8" t="str">
         <f t="shared" si="3"/>
-        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3), c(10.40,6.3,10.41,5.31,2.9), c(F,T,F,T,F), c(3,7,3,3,7),</v>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3), c(4.55,13.17,4.43,0.0,7.44), c(T,T,T,T,F), c(7,3,3,3,8),</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>4</v>
-      </c>
       <c r="B9" s="2">
-        <v>0.47430555555555554</v>
+        <v>9.375E-2</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G9">
         <f t="shared" ref="G9:G14" si="20">IF(A9="",G8,A9)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="str">
         <f t="shared" ref="H9:H14" si="21">HOUR(B9)&amp;"."&amp;MINUTE(B9)</f>
-        <v>11.23</v>
+        <v>2.15</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" ref="I9:I14" si="22">IF(C9="Rams","T","F")</f>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="J9">
         <f t="shared" ref="J9:J14" si="23">SUM(E9:F9)-SUM(E8:F8)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K14" si="24">K8&amp;","&amp;G9</f>
-        <v>2,2,3,3,3,4</v>
+        <v>1,2,2,2,3,3</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" ref="L9:L14" si="25">L8&amp;","&amp;H9</f>
-        <v>10.40,6.3,10.41,5.31,2.9,11.23</v>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15</v>
       </c>
       <c r="M9" t="str">
         <f t="shared" ref="M9:M14" si="26">M8&amp;","&amp;I9</f>
-        <v>F,T,F,T,F,T</v>
+        <v>T,T,T,T,F,F</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" ref="N9:N14" si="27">N8&amp;","&amp;J9</f>
-        <v>3,7,3,3,7,3</v>
+        <v>7,3,3,3,8,8</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" si="3"/>
-        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4), c(10.40,6.3,10.41,5.31,2.9,11.23), c(F,T,F,T,F,T), c(3,7,3,3,7,3),</v>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3), c(4.55,13.17,4.43,0.0,7.44,2.15), c(T,T,T,T,F,F), c(7,3,3,3,8,8),</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>4</v>
+      </c>
       <c r="B10" s="2">
-        <v>6.8750000000000006E-2</v>
+        <v>0.3611111111111111</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G10">
         <f t="shared" si="20"/>
@@ -932,63 +929,60 @@
       </c>
       <c r="H10" t="str">
         <f t="shared" si="21"/>
-        <v>1.39</v>
+        <v>8.40</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="22"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="J10">
         <f t="shared" si="23"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="24"/>
-        <v>2,2,3,3,3,4,4</v>
+        <v>1,2,2,2,3,3,4</v>
       </c>
       <c r="L10" t="str">
         <f t="shared" si="25"/>
-        <v>10.40,6.3,10.41,5.31,2.9,11.23,1.39</v>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15,8.40</v>
       </c>
       <c r="M10" t="str">
         <f t="shared" si="26"/>
-        <v>F,T,F,T,F,T,F</v>
+        <v>T,T,T,T,F,F,T</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="27"/>
-        <v>3,7,3,3,7,3,7</v>
+        <v>7,3,3,3,8,8,3</v>
       </c>
       <c r="O10" t="str">
         <f t="shared" si="3"/>
-        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39), c(F,T,F,T,F,T,F), c(3,7,3,3,7,3,7),</v>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40), c(T,T,T,T,F,F,T), c(7,3,3,3,8,8,3),</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>3</v>
-      </c>
       <c r="B11" s="2">
-        <v>0.24722222222222223</v>
+        <v>0.20069444444444445</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G11">
         <f t="shared" si="20"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" t="str">
         <f t="shared" si="21"/>
-        <v>5.56</v>
+        <v>4.49</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="22"/>
@@ -1000,43 +994,40 @@
       </c>
       <c r="K11" t="str">
         <f t="shared" si="24"/>
-        <v>2,2,3,3,3,4,4,3</v>
+        <v>1,2,2,2,3,3,4,4</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="25"/>
-        <v>10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56</v>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49</v>
       </c>
       <c r="M11" t="str">
         <f t="shared" si="26"/>
-        <v>F,T,F,T,F,T,F,F</v>
+        <v>T,T,T,T,F,F,T,F</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="27"/>
-        <v>3,7,3,3,7,3,7,7</v>
+        <v>7,3,3,3,8,8,3,7</v>
       </c>
       <c r="O11" t="str">
         <f t="shared" si="3"/>
-        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4,3), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56), c(F,T,F,T,F,T,F,F), c(3,7,3,3,7,3,7,7),</v>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4,4), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49), c(T,T,T,T,F,F,T,F), c(7,3,3,3,8,8,3,7),</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>4</v>
-      </c>
       <c r="B12" s="2">
-        <v>0.56874999999999998</v>
+        <v>0.15138888888888888</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12">
         <v>26</v>
       </c>
-      <c r="E12">
-        <v>33</v>
-      </c>
       <c r="F12">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G12">
         <f t="shared" si="20"/>
@@ -1044,7 +1035,7 @@
       </c>
       <c r="H12" t="str">
         <f t="shared" si="21"/>
-        <v>13.39</v>
+        <v>3.38</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="22"/>
@@ -1056,40 +1047,40 @@
       </c>
       <c r="K12" t="str">
         <f t="shared" si="24"/>
-        <v>2,2,3,3,3,4,4,3,4</v>
+        <v>1,2,2,2,3,3,4,4,4</v>
       </c>
       <c r="L12" t="str">
         <f t="shared" si="25"/>
-        <v>10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39</v>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38</v>
       </c>
       <c r="M12" t="str">
         <f t="shared" si="26"/>
-        <v>F,T,F,T,F,T,F,F,T</v>
+        <v>T,T,T,T,F,F,T,F,T</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="27"/>
-        <v>3,7,3,3,7,3,7,7,7</v>
+        <v>7,3,3,3,8,8,3,7,7</v>
       </c>
       <c r="O12" t="str">
         <f t="shared" si="3"/>
-        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4,3,4), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39), c(F,T,F,T,F,T,F,F,T), c(3,7,3,3,7,3,7,7,7),</v>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4,4,4), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38), c(T,T,T,T,F,F,T,F,T), c(7,3,3,3,8,8,3,7,7),</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
-        <v>0.32500000000000001</v>
+        <v>3.2638888888888891E-2</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E13">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F13">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G13">
         <f t="shared" si="20"/>
@@ -1097,52 +1088,52 @@
       </c>
       <c r="H13" t="str">
         <f t="shared" si="21"/>
-        <v>7.48</v>
+        <v>0.47</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="22"/>
-        <v>T</v>
+        <v>F</v>
       </c>
       <c r="J13">
         <f t="shared" si="23"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="24"/>
-        <v>2,2,3,3,3,4,4,3,4,4</v>
+        <v>1,2,2,2,3,3,4,4,4,4</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="25"/>
-        <v>10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39,7.48</v>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47</v>
       </c>
       <c r="M13" t="str">
         <f t="shared" si="26"/>
-        <v>F,T,F,T,F,T,F,F,T,T</v>
+        <v>T,T,T,T,F,F,T,F,T,F</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="27"/>
-        <v>3,7,3,3,7,3,7,7,7,8</v>
+        <v>7,3,3,3,8,8,3,7,7,7</v>
       </c>
       <c r="O13" t="str">
         <f t="shared" si="3"/>
-        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4,3,4,4), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39,7.48), c(F,T,F,T,F,T,F,F,T,T), c(3,7,3,3,7,3,7,7,7,8),</v>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4,4,4,4), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47), c(T,T,T,T,F,F,T,F,T,F), c(7,3,3,3,8,8,3,7,7,7),</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B14" s="2">
-        <v>0.2298611111111111</v>
+        <v>2.6388888888888889E-2</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F14">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G14">
         <f t="shared" si="20"/>
@@ -1150,128 +1141,417 @@
       </c>
       <c r="H14" t="str">
         <f t="shared" si="21"/>
-        <v>5.31</v>
+        <v>0.38</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="22"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="J14">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="24"/>
-        <v>2,2,3,3,3,4,4,3,4,4,4</v>
+        <v>1,2,2,2,3,3,4,4,4,4,4</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="25"/>
-        <v>10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39,7.48,5.31</v>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38</v>
       </c>
       <c r="M14" t="str">
         <f t="shared" si="26"/>
-        <v>F,T,F,T,F,T,F,F,T,T,F</v>
+        <v>T,T,T,T,F,F,T,F,T,F,T</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="27"/>
-        <v>3,7,3,3,7,3,7,7,7,8,3</v>
+        <v>7,3,3,3,8,8,3,7,7,7,9</v>
       </c>
       <c r="O14" t="str">
         <f t="shared" si="3"/>
-        <v>'2012.17.30122012.Away.Seahawks', c(2,2,3,3,3,4,4,3,4,4,4), c(10.40,6.3,10.41,5.31,2.9,11.23,1.39,5.56,13.39,7.48,5.31), c(F,T,F,T,F,T,F,F,T,T,F), c(3,7,3,3,7,3,7,7,7,8,3),</v>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4,4,4,4,4), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38), c(T,T,T,T,F,F,T,F,T,F,T), c(7,3,3,3,8,8,3,7,7,7,9),</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B15" s="2"/>
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.13402777777777777</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15">
+        <v>37</v>
+      </c>
+      <c r="F15">
+        <v>38</v>
+      </c>
+      <c r="G15">
+        <f t="shared" ref="G15" si="28">IF(A15="",G14,A15)</f>
+        <v>5</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" ref="H15" si="29">HOUR(B15)&amp;"."&amp;MINUTE(B15)</f>
+        <v>3.13</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" ref="I15" si="30">IF(C15="Rams","T","F")</f>
+        <v>F</v>
+      </c>
+      <c r="J15">
+        <f t="shared" ref="J15" si="31">SUM(E15:F15)-SUM(E14:F14)</f>
+        <v>10</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" ref="K15" si="32">K14&amp;","&amp;G15</f>
+        <v>1,2,2,2,3,3,4,4,4,4,4,5</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" ref="L15" si="33">L14&amp;","&amp;H15</f>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" ref="M15" si="34">M14&amp;","&amp;I15</f>
+        <v>T,T,T,T,F,F,T,F,T,F,T,F</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" ref="N15" si="35">N14&amp;","&amp;J15</f>
+        <v>7,3,3,3,8,8,3,7,7,7,9,10</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" ref="O15" si="36">"'"&amp;$A$1&amp;"."&amp;$B$1&amp;"."&amp;$H$1&amp;"."&amp;$F$1&amp;"."&amp;$E$1&amp;"', c("&amp;K15&amp;"), c("&amp;L15&amp;"), c("&amp;M15&amp;"), c("&amp;N15&amp;"),"</f>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4,4,4,4,4,5), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13), c(T,T,T,T,F,F,T,F,T,F,T,F), c(7,3,3,3,8,8,3,7,7,7,9,10),</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B18" s="2"/>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O22" s="4" t="s">
+      <c r="B16" s="2">
+        <v>0.1125</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16">
+        <v>34</v>
+      </c>
+      <c r="F16">
+        <v>41</v>
+      </c>
+      <c r="G16">
+        <f t="shared" ref="G16:G17" si="37">IF(A16="",G15,A16)</f>
+        <v>5</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" ref="H16:H17" si="38">HOUR(B16)&amp;"."&amp;MINUTE(B16)</f>
+        <v>2.42</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" ref="I16:I17" si="39">IF(C16="Rams","T","F")</f>
+        <v>F</v>
+      </c>
+      <c r="J16">
+        <f t="shared" ref="J16:J17" si="40">SUM(E16:F16)-SUM(E15:F15)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" ref="K16:K17" si="41">K15&amp;","&amp;G16</f>
+        <v>1,2,2,2,3,3,4,4,4,4,4,5,5</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" ref="L16:L17" si="42">L15&amp;","&amp;H16</f>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13,2.42</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" ref="M16:M17" si="43">M15&amp;","&amp;I16</f>
+        <v>T,T,T,T,F,F,T,F,T,F,T,F,F</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" ref="N16:N17" si="44">N15&amp;","&amp;J16</f>
+        <v>7,3,3,3,8,8,3,7,7,7,9,10,0</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" ref="O16:O17" si="45">"'"&amp;$A$1&amp;"."&amp;$B$1&amp;"."&amp;$H$1&amp;"."&amp;$F$1&amp;"."&amp;$E$1&amp;"', c("&amp;K16&amp;"), c("&amp;L16&amp;"), c("&amp;M16&amp;"), c("&amp;N16&amp;"),"</f>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4,4,4,4,4,5,5), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13,2.42), c(T,T,T,T,F,F,T,F,T,F,T,F,F), c(7,3,3,3,8,8,3,7,7,7,9,10,0),</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.32083333333333336</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17">
+        <v>31</v>
+      </c>
+      <c r="F17">
+        <v>37</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="37"/>
+        <v>5</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="38"/>
+        <v>7.42</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="39"/>
+        <v>F</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="40"/>
+        <v>-7</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="41"/>
+        <v>1,2,2,2,3,3,4,4,4,4,4,5,5,5</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="42"/>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13,2.42,7.42</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="43"/>
+        <v>T,T,T,T,F,F,T,F,T,F,T,F,F,F</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="44"/>
+        <v>7,3,3,3,8,8,3,7,7,7,9,10,0,-7</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="45"/>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4,4,4,4,4,5,5,5), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13,2.42,7.42), c(T,T,T,T,F,F,T,F,T,F,T,F,F,F), c(7,3,3,3,8,8,3,7,7,7,9,10,0,-7),</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B18" s="2">
+        <v>0.1076388888888889</v>
+      </c>
+      <c r="C18" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O23" s="4" t="s">
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>48</v>
+      </c>
+      <c r="F18">
+        <v>40</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ref="G18:G20" si="46">IF(A18="",G17,A18)</f>
+        <v>5</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" ref="H18:H20" si="47">HOUR(B18)&amp;"."&amp;MINUTE(B18)</f>
+        <v>2.35</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" ref="I18:I20" si="48">IF(C18="Rams","T","F")</f>
+        <v>F</v>
+      </c>
+      <c r="J18">
+        <f t="shared" ref="J18:J20" si="49">SUM(E18:F18)-SUM(E17:F17)</f>
+        <v>20</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" ref="K18:K20" si="50">K17&amp;","&amp;G18</f>
+        <v>1,2,2,2,3,3,4,4,4,4,4,5,5,5,5</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" ref="L18:L20" si="51">L17&amp;","&amp;H18</f>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13,2.42,7.42,2.35</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" ref="M18:M20" si="52">M17&amp;","&amp;I18</f>
+        <v>T,T,T,T,F,F,T,F,T,F,T,F,F,F,F</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" ref="N18:N20" si="53">N17&amp;","&amp;J18</f>
+        <v>7,3,3,3,8,8,3,7,7,7,9,10,0,-7,20</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" ref="O18:O20" si="54">"'"&amp;$A$1&amp;"."&amp;$B$1&amp;"."&amp;$H$1&amp;"."&amp;$F$1&amp;"."&amp;$E$1&amp;"', c("&amp;K18&amp;"), c("&amp;L18&amp;"), c("&amp;M18&amp;"), c("&amp;N18&amp;"),"</f>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4,4,4,4,4,5,5,5,5), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13,2.42,7.42,2.35), c(T,T,T,T,F,F,T,F,T,F,T,F,F,F,F), c(7,3,3,3,8,8,3,7,7,7,9,10,0,-7,20),</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B19" s="2">
+        <v>4.583333333333333E-2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O24" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O25" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O26" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O27" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O28" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O29" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O30" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O31" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O32" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="E19">
+        <v>55</v>
+      </c>
+      <c r="F19">
+        <v>40</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="46"/>
+        <v>5</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="47"/>
+        <v>1.6</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="48"/>
+        <v>F</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="49"/>
+        <v>7</v>
+      </c>
+      <c r="K19" t="str">
+        <f t="shared" si="50"/>
+        <v>1,2,2,2,3,3,4,4,4,4,4,5,5,5,5,5</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="51"/>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13,2.42,7.42,2.35,1.6</v>
+      </c>
+      <c r="M19" t="str">
+        <f t="shared" si="52"/>
+        <v>T,T,T,T,F,F,T,F,T,F,T,F,F,F,F,F</v>
+      </c>
+      <c r="N19" t="str">
+        <f t="shared" si="53"/>
+        <v>7,3,3,3,8,8,3,7,7,7,9,10,0,-7,20,7</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="54"/>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4,4,4,4,4,5,5,5,5,5), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13,2.42,7.42,2.35,1.6), c(T,T,T,T,F,F,T,F,T,F,T,F,F,F,F,F), c(7,3,3,3,8,8,3,7,7,7,9,10,0,-7,20,7),</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B20" s="2">
+        <v>7.5694444444444439E-2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20">
+        <v>51</v>
+      </c>
+      <c r="F20">
+        <v>54</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="46"/>
+        <v>5</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="47"/>
+        <v>1.49</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="48"/>
+        <v>T</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="49"/>
+        <v>10</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="50"/>
+        <v>1,2,2,2,3,3,4,4,4,4,4,5,5,5,5,5,5</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="51"/>
+        <v>4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13,2.42,7.42,2.35,1.6,1.49</v>
+      </c>
+      <c r="M20" t="str">
+        <f t="shared" si="52"/>
+        <v>T,T,T,T,F,F,T,F,T,F,T,F,F,F,F,F,T</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="53"/>
+        <v>7,3,3,3,8,8,3,7,7,7,9,10,0,-7,20,7,10</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="54"/>
+        <v>'2026.3.27092026.Away.Broncos', c(1,2,2,2,3,3,4,4,4,4,4,5,5,5,5,5,5), c(4.55,13.17,4.43,0.0,7.44,2.15,8.40,4.49,3.38,0.47,0.38,3.13,2.42,7.42,2.35,1.6,1.49), c(T,T,T,T,F,F,T,F,T,F,T,F,F,F,F,F,T), c(7,3,3,3,8,8,3,7,7,7,9,10,0,-7,20,7,10),</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="5"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="5"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="5"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="5"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="5"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="6"/>
     </row>
     <row r="33" spans="15:15" x14ac:dyDescent="0.2">
-      <c r="O33" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="O33" s="6"/>
     </row>
     <row r="34" spans="15:15" x14ac:dyDescent="0.2">
-      <c r="O34" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="O34" s="6"/>
     </row>
     <row r="35" spans="15:15" x14ac:dyDescent="0.2">
-      <c r="O35" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="O35" s="6"/>
     </row>
     <row r="36" spans="15:15" x14ac:dyDescent="0.2">
-      <c r="O36" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="O36" s="5"/>
     </row>
     <row r="37" spans="15:15" x14ac:dyDescent="0.2">
-      <c r="O37" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="O37" s="5"/>
+    </row>
+    <row r="38" spans="15:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">
